--- a/master/result/17_豪门弃女：步步惊心/17_豪门步步惊心.xlsx
+++ b/master/result/17_豪门弃女：步步惊心/17_豪门步步惊心.xlsx
@@ -397,588 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>background</v>
       </c>
       <c r="B2" t="str">
-        <v>background</v>
+        <v>/ˈbaækɡraʊnd/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>背景</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>kitchen</v>
       </c>
       <c r="B3" t="str">
-        <v>kitchen</v>
+        <v>/kitchen/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>厨房</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>broom</v>
       </c>
       <c r="B4" t="str">
-        <v>broom</v>
+        <v>/bruːm/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>扫帚</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>gentleman</v>
       </c>
       <c r="B5" t="str">
-        <v>gentleman</v>
+        <v>/gentleman/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>绅士</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>dam</v>
       </c>
       <c r="B6" t="str">
-        <v>dam</v>
+        <v>/dam/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>水坝</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>oak</v>
       </c>
       <c r="B7" t="str">
-        <v>oak</v>
+        <v>/oak/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>橡树</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>pronounce</v>
       </c>
       <c r="B8" t="str">
-        <v>pronounce</v>
+        <v>/prəˈnaʊns/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>宣布</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>minimum</v>
       </c>
       <c r="B9" t="str">
-        <v>minimum</v>
+        <v>/minimum/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>最低限度</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>interim</v>
       </c>
       <c r="B10" t="str">
-        <v>interim</v>
+        <v>/interim/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>临时</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>bitter</v>
       </c>
       <c r="B11" t="str">
-        <v>bitter</v>
+        <v>/bitter/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>苦涩</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>constitution</v>
       </c>
       <c r="B12" t="str">
-        <v>constitution</v>
+        <v>/ˌkɒnstɪˈtjuːʃn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>体格</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>beware</v>
       </c>
       <c r="B13" t="str">
-        <v>beware</v>
+        <v>/beware/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>当心</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>biography</v>
       </c>
       <c r="B14" t="str">
-        <v>biography</v>
+        <v>/biography/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>传记</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>pilgrim</v>
       </c>
       <c r="B15" t="str">
-        <v>pilgrim</v>
+        <v>/pilgrim/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>朝圣者</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>auto</v>
       </c>
       <c r="B16" t="str">
-        <v>auto</v>
+        <v>/auto/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>汽车</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>thin</v>
       </c>
       <c r="B17" t="str">
-        <v>thin</v>
+        <v>/thin/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>瘦削</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>reading</v>
       </c>
       <c r="B18" t="str">
-        <v>reading</v>
+        <v>/reading/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>阅读</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>artificial</v>
       </c>
       <c r="B19" t="str">
-        <v>artificial</v>
+        <v>/artificial/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>人为的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>chain</v>
       </c>
       <c r="B20" t="str">
-        <v>chain</v>
+        <v>/tʃeɪn/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>链条</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>militant</v>
       </c>
       <c r="B21" t="str">
-        <v>militant</v>
+        <v>/militant/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>好战的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>indeed</v>
       </c>
       <c r="B22" t="str">
-        <v>indeed</v>
+        <v>/indeed/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>确实</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>skeleton</v>
       </c>
       <c r="B23" t="str">
-        <v>skeleton</v>
+        <v>/skeleton/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>骨架</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>warm</v>
       </c>
       <c r="B24" t="str">
-        <v>warm</v>
+        <v>/warm/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>温暖</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>precaution</v>
       </c>
       <c r="B25" t="str">
-        <v>precaution</v>
+        <v>/precaution/</v>
       </c>
       <c r="C25" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>预防</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>communicate</v>
       </c>
       <c r="B26" t="str">
-        <v>communicate</v>
+        <v>/kəˈmjuːnɪkeɪt/</v>
       </c>
       <c r="C26" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D26" t="str">
         <v>交流</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>foot</v>
       </c>
       <c r="B27" t="str">
-        <v>foot</v>
+        <v>/foot/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>脚步</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>revelation</v>
       </c>
       <c r="B28" t="str">
-        <v>revelation</v>
+        <v>/revelation/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>揭露</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>console</v>
       </c>
       <c r="B29" t="str">
-        <v>console</v>
+        <v>/console/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>控制台</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>mend</v>
       </c>
       <c r="B30" t="str">
-        <v>mend</v>
+        <v>/mend/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>修复</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>cry</v>
       </c>
       <c r="B31" t="str">
-        <v>cry</v>
+        <v>/kraɪ/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>哭</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>satire</v>
       </c>
       <c r="B32" t="str">
-        <v>satire</v>
+        <v>/satire/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>讽刺</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>which</v>
       </c>
       <c r="B33" t="str">
-        <v>which</v>
+        <v>/which/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>哪些</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>afterward</v>
       </c>
       <c r="B34" t="str">
-        <v>afterward</v>
+        <v>/afterward/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>后来</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>fame</v>
       </c>
       <c r="B35" t="str">
+        <v>/fame/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>名声</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>adequate</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/ˈædɪkwət/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>充足</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>zoo</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/zoo/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>动物园</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>tropical</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/tropical/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>热带</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>peanut</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/peanut/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>花生</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>guidance</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/guidance/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>指导</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>intact</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/intact/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>完整无缺</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>tight</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/tight/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>紧张</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>pocket</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/pocket/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>装进口袋</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>voyage</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/voyage/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>航行</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>steward</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/steward/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>乘务员</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>pool</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/pool/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>合伙经营</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>class</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/class/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>阶层</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>heave</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/heave/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>举起</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Christ</v>
+      </c>
+      <c r="B49" t="str">
+        <v>/Christ/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>基督</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>mixture</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/mixture/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>混合物</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
         <v>fame</v>
       </c>
-      <c r="C35" t="str">
-        <v>名声</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>adequate</v>
-      </c>
-      <c r="C36" t="str">
-        <v>充足</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>zoo</v>
-      </c>
-      <c r="C37" t="str">
-        <v>动物园</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>tropical</v>
-      </c>
-      <c r="C38" t="str">
-        <v>热带</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>peanut</v>
-      </c>
-      <c r="C39" t="str">
-        <v>花生</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>guidance</v>
-      </c>
-      <c r="C40" t="str">
-        <v>指导</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>intact</v>
-      </c>
-      <c r="C41" t="str">
-        <v>完整无缺</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>tight</v>
-      </c>
-      <c r="C42" t="str">
-        <v>紧张</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>pocket</v>
-      </c>
-      <c r="C43" t="str">
-        <v>装进口袋</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>voyage</v>
-      </c>
-      <c r="C44" t="str">
-        <v>航行</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>steward</v>
-      </c>
-      <c r="C45" t="str">
-        <v>乘务员</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>pool</v>
-      </c>
-      <c r="C46" t="str">
-        <v>合伙经营</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>class</v>
-      </c>
-      <c r="C47" t="str">
-        <v>阶层</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>heave</v>
-      </c>
-      <c r="C48" t="str">
-        <v>举起</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Christ</v>
-      </c>
-      <c r="C49" t="str">
-        <v>基督</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>mixture</v>
-      </c>
-      <c r="C50" t="str">
-        <v>混合物</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
       <c r="B51" t="str">
-        <v>fame</v>
+        <v>/fame/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>名望</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>condemn</v>
       </c>
       <c r="B52" t="str">
-        <v>condemn</v>
+        <v>/condemn/</v>
       </c>
       <c r="C52" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D52" t="str">
         <v>谴责</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>